--- a/test/moe_w4a8/gemm2_prefill_tuning/moegemmoutput.xlsx
+++ b/test/moe_w4a8/gemm2_prefill_tuning/moegemmoutput.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
         <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>1648.032066345215</v>
+        <v>1668.370969772339</v>
       </c>
     </row>
     <row r="3">
@@ -497,7 +497,7 @@
         <v>128</v>
       </c>
       <c r="F3" t="n">
-        <v>1819.92760848999</v>
+        <v>1809.774782180786</v>
       </c>
     </row>
     <row r="4">
@@ -517,107 +517,7 @@
         <v>128</v>
       </c>
       <c r="F4" t="n">
-        <v>2267.662660598755</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2048</v>
-      </c>
-      <c r="B5" t="n">
-        <v>512</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3584</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E5" t="n">
-        <v>128</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3415.589294433594</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4096</v>
-      </c>
-      <c r="B6" t="n">
-        <v>512</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3584</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E6" t="n">
-        <v>128</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6047.822906494141</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6144</v>
-      </c>
-      <c r="B7" t="n">
-        <v>512</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3584</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E7" t="n">
-        <v>128</v>
-      </c>
-      <c r="F7" t="n">
-        <v>11731.10999298096</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>8192</v>
-      </c>
-      <c r="B8" t="n">
-        <v>512</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3584</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E8" t="n">
-        <v>128</v>
-      </c>
-      <c r="F8" t="n">
-        <v>15904.4259185791</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>16384</v>
-      </c>
-      <c r="B9" t="n">
-        <v>512</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3584</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E9" t="n">
-        <v>128</v>
-      </c>
-      <c r="F9" t="n">
-        <v>17675.88375854492</v>
+        <v>2287.08420753479</v>
       </c>
     </row>
   </sheetData>
